--- a/xls/square_16_quad4_16.xlsx
+++ b/xls/square_16_quad4_16.xlsx
@@ -456,6 +456,76 @@
         <v>10</v>
       </c>
     </row>
+    <row r="14" spans="1:11">
+      <c r="A14" t="s">
+        <v>11</v>
+      </c>
+      <c r="B14">
+        <v>289</v>
+      </c>
+      <c r="C14" t="s">
+        <v>11</v>
+      </c>
+      <c r="D14">
+        <v>289</v>
+      </c>
+      <c r="E14" t="s">
+        <v>12</v>
+      </c>
+      <c r="F14">
+        <v>225</v>
+      </c>
+      <c r="G14" t="s">
+        <v>13</v>
+      </c>
+      <c r="H14">
+        <v>588</v>
+      </c>
+      <c r="I14">
+        <v>1.9082817472867573</v>
+      </c>
+      <c r="J14">
+        <v>-0.24159351376338975</v>
+      </c>
+      <c r="K14">
+        <v>0.4948613159730506</v>
+      </c>
+    </row>
+    <row r="15" spans="1:11">
+      <c r="A15" t="s">
+        <v>11</v>
+      </c>
+      <c r="B15">
+        <v>289</v>
+      </c>
+      <c r="C15" t="s">
+        <v>11</v>
+      </c>
+      <c r="D15">
+        <v>289</v>
+      </c>
+      <c r="E15" t="s">
+        <v>12</v>
+      </c>
+      <c r="F15">
+        <v>256</v>
+      </c>
+      <c r="G15" t="s">
+        <v>13</v>
+      </c>
+      <c r="H15">
+        <v>675</v>
+      </c>
+      <c r="I15">
+        <v>0.7255821913590071</v>
+      </c>
+      <c r="J15">
+        <v>-0.7013892416764353</v>
+      </c>
+      <c r="K15">
+        <v>0.047494411202151095</v>
+      </c>
+    </row>
     <row r="16" spans="1:11">
       <c r="A16" t="s">
         <v>11</v>
@@ -482,13 +552,13 @@
         <v>768</v>
       </c>
       <c r="I16">
-        <v>1.8822196190679998</v>
+        <v>1.068577725380464</v>
       </c>
       <c r="J16">
-        <v>-1.243177486574158</v>
+        <v>-1.3741805692515263</v>
       </c>
       <c r="K16">
-        <v>-0.04550440664616511</v>
+        <v>-0.38904535623320824</v>
       </c>
     </row>
     <row r="17" spans="1:11">
@@ -517,13 +587,13 @@
         <v>867</v>
       </c>
       <c r="I17">
-        <v>-1.8399779207379072</v>
+        <v>-1.4859902537850649</v>
       </c>
       <c r="J17">
-        <v>-1.8449635376923605</v>
+        <v>-1.5256319852761573</v>
       </c>
       <c r="K17">
-        <v>-0.3641923512277838</v>
+        <v>0.3180216404992794</v>
       </c>
     </row>
     <row r="18" spans="1:11">
@@ -552,13 +622,13 @@
         <v>972</v>
       </c>
       <c r="I18">
-        <v>-1.8777080110648685</v>
+        <v>-1.5439991107745332</v>
       </c>
       <c r="J18">
-        <v>-1.8849853768381137</v>
+        <v>-1.5896946708416113</v>
       </c>
       <c r="K18">
-        <v>0.7590802354434127</v>
+        <v>1.887510784377386</v>
       </c>
     </row>
     <row r="19" spans="1:11">
@@ -587,13 +657,13 @@
         <v>1083</v>
       </c>
       <c r="I19">
-        <v>-1.8695597720308776</v>
+        <v>-1.4630143959911082</v>
       </c>
       <c r="J19">
-        <v>-1.8629377472144921</v>
+        <v>-1.5540518841468862</v>
       </c>
       <c r="K19">
-        <v>1.4538136817857115</v>
+        <v>2.7736057864963493</v>
       </c>
     </row>
     <row r="20" spans="1:11">
@@ -622,13 +692,13 @@
         <v>1200</v>
       </c>
       <c r="I20">
-        <v>-1.859353955107669</v>
+        <v>-1.5592381167704712</v>
       </c>
       <c r="J20">
-        <v>-1.8547319154053394</v>
+        <v>-1.6167671107350394</v>
       </c>
       <c r="K20">
-        <v>1.793807148566275</v>
+        <v>3.8695794991268335</v>
       </c>
     </row>
     <row r="21" spans="1:11">
@@ -657,13 +727,13 @@
         <v>1323</v>
       </c>
       <c r="I21">
-        <v>-1.8091587383503787</v>
+        <v>-0.7052747847801428</v>
       </c>
       <c r="J21">
-        <v>-1.7283694120523576</v>
+        <v>-0.6586013481831127</v>
       </c>
       <c r="K21">
-        <v>2.90335396458534</v>
+        <v>4.807966825595313</v>
       </c>
     </row>
     <row r="22" spans="1:11">
@@ -692,13 +762,13 @@
         <v>1452</v>
       </c>
       <c r="I22">
-        <v>-1.3604791567850054</v>
+        <v>-0.20619510205729696</v>
       </c>
       <c r="J22">
-        <v>-0.9809886977811675</v>
+        <v>-0.19713822313645743</v>
       </c>
       <c r="K22">
-        <v>3.5668907710277065</v>
+        <v>4.882235161406463</v>
       </c>
     </row>
     <row r="23" spans="1:11">
@@ -727,13 +797,13 @@
         <v>1587</v>
       </c>
       <c r="I23">
-        <v>-0.8906371433195535</v>
+        <v>-0.03882526748940543</v>
       </c>
       <c r="J23">
-        <v>-0.7109769747364552</v>
+        <v>-0.03739503250150823</v>
       </c>
       <c r="K23">
-        <v>3.848710411589667</v>
+        <v>4.633342950077987</v>
       </c>
     </row>
     <row r="24" spans="1:11">
@@ -762,13 +832,13 @@
         <v>1728</v>
       </c>
       <c r="I24">
-        <v>-0.07599676506207693</v>
+        <v>-0.0034107056949706886</v>
       </c>
       <c r="J24">
-        <v>-0.0606646572253335</v>
+        <v>-0.002814480273291768</v>
       </c>
       <c r="K24">
-        <v>3.3372122722925557</v>
+        <v>4.090821899510907</v>
       </c>
     </row>
     <row r="25" spans="1:11">
@@ -797,13 +867,13 @@
         <v>1875</v>
       </c>
       <c r="I25">
-        <v>-0.002793732192859586</v>
+        <v>-2.5741915981740357e-5</v>
       </c>
       <c r="J25">
-        <v>-0.0025003125129071995</v>
+        <v>-2.3031217844375907e-5</v>
       </c>
       <c r="K25">
-        <v>3.1354152052398034</v>
+        <v>3.094411893659914</v>
       </c>
     </row>
     <row r="26" spans="1:11">
@@ -832,13 +902,13 @@
         <v>2028</v>
       </c>
       <c r="I26">
-        <v>-0.001398654923097819</v>
+        <v>-1.3169403869193221e-5</v>
       </c>
       <c r="J26">
-        <v>-0.0012951841986330699</v>
+        <v>-1.2179504855690702e-5</v>
       </c>
       <c r="K26">
-        <v>3.0019069331127306</v>
+        <v>2.9589328900993106</v>
       </c>
     </row>
     <row r="27" spans="1:11">
@@ -867,13 +937,13 @@
         <v>2187</v>
       </c>
       <c r="I27">
-        <v>-0.0008009312022835864</v>
+        <v>-7.577644859597853e-6</v>
       </c>
       <c r="J27">
-        <v>-0.0007611253014159652</v>
+        <v>-7.192039690502713e-6</v>
       </c>
       <c r="K27">
-        <v>2.891924870094484</v>
+        <v>2.846627560634995</v>
       </c>
     </row>
     <row r="28" spans="1:11">
@@ -902,13 +972,13 @@
         <v>2352</v>
       </c>
       <c r="I28">
-        <v>-0.0004931731091258486</v>
+        <v>-4.598118791477423e-6</v>
       </c>
       <c r="J28">
-        <v>-0.000471809562878157</v>
+        <v>-4.399804654373484e-6</v>
       </c>
       <c r="K28">
-        <v>2.7885964778283254</v>
+        <v>2.738383232824322</v>
       </c>
     </row>
     <row r="29" spans="1:11">
@@ -937,13 +1007,13 @@
         <v>2523</v>
       </c>
       <c r="I29">
-        <v>-0.0003330646025726802</v>
+        <v>-3.0198607572114897e-6</v>
       </c>
       <c r="J29">
-        <v>-0.0002949988525115911</v>
+        <v>-2.6859904008630136e-6</v>
       </c>
       <c r="K29">
-        <v>2.67832865321784</v>
+        <v>2.6215942283073956</v>
       </c>
     </row>
     <row r="30" spans="1:11">
@@ -972,13 +1042,13 @@
         <v>2700</v>
       </c>
       <c r="I30">
-        <v>-0.0004239778829835538</v>
+        <v>-3.675508089994329e-6</v>
       </c>
       <c r="J30">
-        <v>-0.00041653051174095096</v>
+        <v>-3.612949714083696e-6</v>
       </c>
       <c r="K30">
-        <v>2.7636079685095325</v>
+        <v>2.6950253914118147</v>
       </c>
     </row>
     <row r="31" spans="1:11">
@@ -1007,13 +1077,13 @@
         <v>2883</v>
       </c>
       <c r="I31">
-        <v>5.2881344864274715e-6</v>
+        <v>3.8705285500005e-8</v>
       </c>
       <c r="J31">
-        <v>7.009234044731508e-7</v>
+        <v>-2.773653626851865e-10</v>
       </c>
       <c r="K31">
-        <v>1.7949927964390047</v>
+        <v>1.7609060972321333</v>
       </c>
     </row>
     <row r="32" spans="1:11">
@@ -1042,13 +1112,13 @@
         <v>3072</v>
       </c>
       <c r="I32">
-        <v>-8.706864267971215e-6</v>
+        <v>-8.870232747193258e-8</v>
       </c>
       <c r="J32">
-        <v>-6.708534087148925e-6</v>
+        <v>-7.206416066894346e-8</v>
       </c>
       <c r="K32">
-        <v>1.7782637745948766</v>
+        <v>1.7787698817932391</v>
       </c>
     </row>
   </sheetData>
